--- a/output/Tables/7000 steps/HIA_age_Rubin_7000steps_1000replicate.xlsx
+++ b/output/Tables/7000 steps/HIA_age_Rubin_7000steps_1000replicate.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>1089.589</v>
+        <v>1067.323</v>
       </c>
       <c r="D2">
-        <v>1010.349</v>
+        <v>989.848</v>
       </c>
       <c r="E2">
-        <v>1168.829</v>
+        <v>1144.798</v>
       </c>
       <c r="F2">
-        <v>62169.073</v>
+        <v>60894.754</v>
       </c>
       <c r="G2">
-        <v>57697.521</v>
+        <v>56524.061</v>
       </c>
       <c r="H2">
-        <v>66640.624</v>
+        <v>65265.447</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>8268486645.352</v>
+        <v>8099002252.642</v>
       </c>
       <c r="M2">
-        <v>7673770275.503</v>
+        <v>7517700109.405</v>
       </c>
       <c r="N2">
-        <v>8863203015.201</v>
+        <v>8680304395.878</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>2385.162</v>
+        <v>2314.291</v>
       </c>
       <c r="D3">
-        <v>2234.06</v>
+        <v>2168.049</v>
       </c>
       <c r="E3">
-        <v>2536.263</v>
+        <v>2460.533</v>
       </c>
       <c r="F3">
-        <v>109952.348</v>
+        <v>106715.689</v>
       </c>
       <c r="G3">
-        <v>103229.63</v>
+        <v>100206.985</v>
       </c>
       <c r="H3">
-        <v>116675.065</v>
+        <v>113224.394</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>14623662223.184</v>
+        <v>14193186690.17</v>
       </c>
       <c r="M3">
-        <v>13729540803.695</v>
+        <v>13327528950.487</v>
       </c>
       <c r="N3">
-        <v>15517783642.673</v>
+        <v>15058844429.852</v>
       </c>
     </row>
     <row r="4">
@@ -534,22 +534,22 @@
         </is>
       </c>
       <c r="C4">
-        <v>7066.891</v>
+        <v>6867.439</v>
       </c>
       <c r="D4">
-        <v>6648.559</v>
+        <v>6462.017</v>
       </c>
       <c r="E4">
-        <v>7485.223</v>
+        <v>7272.862</v>
       </c>
       <c r="F4">
-        <v>258585.035</v>
+        <v>251265.442</v>
       </c>
       <c r="G4">
-        <v>243838.014</v>
+        <v>236972.912</v>
       </c>
       <c r="H4">
-        <v>273332.056</v>
+        <v>265557.972</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>34391809681.536</v>
+        <v>33418303781.208</v>
       </c>
       <c r="M4">
-        <v>32430455865.763</v>
+        <v>31517397261.737</v>
       </c>
       <c r="N4">
-        <v>36353163497.31</v>
+        <v>35319210300.68</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="C5">
-        <v>14322.975</v>
+        <v>14104.115</v>
       </c>
       <c r="D5">
-        <v>13599.59</v>
+        <v>13398.688</v>
       </c>
       <c r="E5">
-        <v>15046.359</v>
+        <v>14809.541</v>
       </c>
       <c r="F5">
-        <v>382163.641</v>
+        <v>376549.961</v>
       </c>
       <c r="G5">
-        <v>363792.214</v>
+        <v>358618.167</v>
       </c>
       <c r="H5">
-        <v>400535.068</v>
+        <v>394481.754</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -609,13 +609,13 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>50827764241.07</v>
+        <v>50081144772.822</v>
       </c>
       <c r="M5">
-        <v>48384364503.899</v>
+        <v>47696216243.302</v>
       </c>
       <c r="N5">
-        <v>53271163978.242</v>
+        <v>52466073302.343</v>
       </c>
     </row>
     <row r="6">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="C6">
-        <v>28291.56</v>
+        <v>27953.694</v>
       </c>
       <c r="D6">
-        <v>26932.732</v>
+        <v>26627.522</v>
       </c>
       <c r="E6">
-        <v>29650.388</v>
+        <v>29279.865</v>
       </c>
       <c r="F6">
-        <v>478434.077</v>
+        <v>472663.879</v>
       </c>
       <c r="G6">
-        <v>456502.352</v>
+        <v>451278.251</v>
       </c>
       <c r="H6">
-        <v>500365.803</v>
+        <v>494049.508</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -657,13 +657,13 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>63631732287.45</v>
+        <v>62864295973.278</v>
       </c>
       <c r="M6">
-        <v>60714812753.646</v>
+        <v>60020007427.96</v>
       </c>
       <c r="N6">
-        <v>66548651821.255</v>
+        <v>65708584518.596</v>
       </c>
     </row>
     <row r="7">
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="C7">
-        <v>42651.973</v>
+        <v>43170.471</v>
       </c>
       <c r="D7">
-        <v>40239.309</v>
+        <v>40785.354</v>
       </c>
       <c r="E7">
-        <v>45064.637</v>
+        <v>45555.589</v>
       </c>
       <c r="F7">
-        <v>310680.48</v>
+        <v>314678.982</v>
       </c>
       <c r="G7">
-        <v>295114.301</v>
+        <v>299299.418</v>
       </c>
       <c r="H7">
-        <v>326246.66</v>
+        <v>330058.545</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>41320503861.969</v>
+        <v>41852304561.409</v>
       </c>
       <c r="M7">
-        <v>39250201989.275</v>
+        <v>39806822597.997</v>
       </c>
       <c r="N7">
-        <v>43390805734.662</v>
+        <v>43897786524.822</v>
       </c>
     </row>
     <row r="8">
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="C8">
-        <v>63117.836</v>
+        <v>71692.099</v>
       </c>
       <c r="D8">
-        <v>58114.951</v>
+        <v>66428.965</v>
       </c>
       <c r="E8">
-        <v>68120.72</v>
+        <v>76955.23299999999</v>
       </c>
       <c r="F8">
-        <v>50146.382</v>
+        <v>55541.192</v>
       </c>
       <c r="G8">
-        <v>44525.152</v>
+        <v>49764.911</v>
       </c>
       <c r="H8">
-        <v>55767.611</v>
+        <v>61317.472</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -753,13 +753,13 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>6669468745.188</v>
+        <v>7386978479.055</v>
       </c>
       <c r="M8">
-        <v>5921845210.215</v>
+        <v>6618733213.023</v>
       </c>
       <c r="N8">
-        <v>7417092280.161</v>
+        <v>8155223745.088</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>763.508</v>
+        <v>668.252</v>
       </c>
       <c r="D9">
-        <v>707.775</v>
+        <v>619.213</v>
       </c>
       <c r="E9">
-        <v>819.24</v>
+        <v>717.2910000000001</v>
       </c>
       <c r="F9">
-        <v>2892.835</v>
+        <v>1439.789</v>
       </c>
       <c r="G9">
-        <v>2679.907</v>
+        <v>1339.737</v>
       </c>
       <c r="H9">
-        <v>3105.763</v>
+        <v>1539.842</v>
       </c>
       <c r="I9">
-        <v>42528906.658</v>
+        <v>35213529.901</v>
       </c>
       <c r="J9">
-        <v>39424500.376</v>
+        <v>32629403.445</v>
       </c>
       <c r="K9">
-        <v>45633312.941</v>
+        <v>37797656.356</v>
       </c>
       <c r="L9">
-        <v>384747088.587</v>
+        <v>191491973.229</v>
       </c>
       <c r="M9">
-        <v>356427651.735</v>
+        <v>178184995.322</v>
       </c>
       <c r="N9">
-        <v>413066525.44</v>
+        <v>204798951.136</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>1805.007</v>
+        <v>1559.823</v>
       </c>
       <c r="D10">
-        <v>1694</v>
+        <v>1463.391</v>
       </c>
       <c r="E10">
-        <v>1916.014</v>
+        <v>1656.256</v>
       </c>
       <c r="F10">
-        <v>5562.222</v>
+        <v>3836.835</v>
       </c>
       <c r="G10">
-        <v>5222.983</v>
+        <v>3608.425</v>
       </c>
       <c r="H10">
-        <v>5901.46</v>
+        <v>4065.246</v>
       </c>
       <c r="I10">
-        <v>100542509.831</v>
+        <v>82194893.30599999</v>
       </c>
       <c r="J10">
-        <v>94359189.43099999</v>
+        <v>77113380.472</v>
       </c>
       <c r="K10">
-        <v>106725830.23</v>
+        <v>87276406.141</v>
       </c>
       <c r="L10">
-        <v>739775487.207</v>
+        <v>510299115.129</v>
       </c>
       <c r="M10">
-        <v>694656804.75</v>
+        <v>479920481.814</v>
       </c>
       <c r="N10">
-        <v>784894169.665</v>
+        <v>540677748.444</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>6891.068</v>
+        <v>6040.737</v>
       </c>
       <c r="D11">
-        <v>6474.674</v>
+        <v>5673.091</v>
       </c>
       <c r="E11">
-        <v>7307.461</v>
+        <v>6408.383</v>
       </c>
       <c r="F11">
-        <v>16958.628</v>
+        <v>13343.459</v>
       </c>
       <c r="G11">
-        <v>15931.742</v>
+        <v>12554.574</v>
       </c>
       <c r="H11">
-        <v>17985.514</v>
+        <v>14132.344</v>
       </c>
       <c r="I11">
-        <v>383846256.509</v>
+        <v>318316631.306</v>
       </c>
       <c r="J11">
-        <v>360652316.131</v>
+        <v>298943529.613</v>
       </c>
       <c r="K11">
-        <v>407040196.888</v>
+        <v>337689732.999</v>
       </c>
       <c r="L11">
-        <v>2255497506.657</v>
+        <v>1774680036.279</v>
       </c>
       <c r="M11">
-        <v>2118921632.968</v>
+        <v>1669758346.931</v>
       </c>
       <c r="N11">
-        <v>2392073380.345</v>
+        <v>1879601725.628</v>
       </c>
     </row>
     <row r="12">
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>15336.134</v>
+        <v>13544.21</v>
       </c>
       <c r="D12">
-        <v>14558.79</v>
+        <v>12858.114</v>
       </c>
       <c r="E12">
-        <v>16113.479</v>
+        <v>14230.306</v>
       </c>
       <c r="F12">
-        <v>27521.729</v>
+        <v>25556.105</v>
       </c>
       <c r="G12">
-        <v>26138.558</v>
+        <v>24297.693</v>
       </c>
       <c r="H12">
-        <v>28904.901</v>
+        <v>26814.516</v>
       </c>
       <c r="I12">
-        <v>854253358.4579999</v>
+        <v>713712136.806</v>
       </c>
       <c r="J12">
-        <v>810953714.522</v>
+        <v>677558323.8150001</v>
       </c>
       <c r="K12">
-        <v>897553002.393</v>
+        <v>749865949.7970001</v>
       </c>
       <c r="L12">
-        <v>3660390009.236</v>
+        <v>3398961903.515</v>
       </c>
       <c r="M12">
-        <v>3476428184.987</v>
+        <v>3231593113.869</v>
       </c>
       <c r="N12">
-        <v>3844351833.485</v>
+        <v>3566330693.161</v>
       </c>
     </row>
     <row r="13">
@@ -966,40 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>41291.125</v>
+        <v>36436.827</v>
       </c>
       <c r="D13">
-        <v>39301.079</v>
+        <v>34693.709</v>
       </c>
       <c r="E13">
-        <v>43281.171</v>
+        <v>38179.946</v>
       </c>
       <c r="F13">
-        <v>48536.693</v>
+        <v>50696.27</v>
       </c>
       <c r="G13">
-        <v>46163.913</v>
+        <v>48294.081</v>
       </c>
       <c r="H13">
-        <v>50909.473</v>
+        <v>53098.459</v>
       </c>
       <c r="I13">
-        <v>2299998253.221</v>
+        <v>1920038622.128</v>
       </c>
       <c r="J13">
-        <v>2189148711.921</v>
+        <v>1828184969.75</v>
       </c>
       <c r="K13">
-        <v>2410847794.52</v>
+        <v>2011892274.506</v>
       </c>
       <c r="L13">
-        <v>6455380191.374</v>
+        <v>6742603906.25</v>
       </c>
       <c r="M13">
-        <v>6139800445.323</v>
+        <v>6423112714.755</v>
       </c>
       <c r="N13">
-        <v>6770959937.425</v>
+        <v>7062095097.745</v>
       </c>
     </row>
     <row r="14">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="C14">
-        <v>45931.892</v>
+        <v>41516.973</v>
       </c>
       <c r="D14">
-        <v>43541.45</v>
+        <v>39390.051</v>
       </c>
       <c r="E14">
-        <v>48322.335</v>
+        <v>43643.895</v>
       </c>
       <c r="F14">
-        <v>26367.006</v>
+        <v>51193.627</v>
       </c>
       <c r="G14">
-        <v>24930.789</v>
+        <v>48539.14</v>
       </c>
       <c r="H14">
-        <v>27803.223</v>
+        <v>53848.115</v>
       </c>
       <c r="I14">
-        <v>2558498272.131</v>
+        <v>2187736879.708</v>
       </c>
       <c r="J14">
-        <v>2425345828.79</v>
+        <v>2075658718.248</v>
       </c>
       <c r="K14">
-        <v>2691650715.472</v>
+        <v>2299815041.167</v>
       </c>
       <c r="L14">
-        <v>3506811803.288</v>
+        <v>6808752443.391</v>
       </c>
       <c r="M14">
-        <v>3315794927.957</v>
+        <v>6455705635.247</v>
       </c>
       <c r="N14">
-        <v>3697828678.618</v>
+        <v>7161799251.535</v>
       </c>
     </row>
     <row r="15">
@@ -1062,40 +1062,40 @@
         </is>
       </c>
       <c r="C15">
-        <v>33852.655</v>
+        <v>33842.63</v>
       </c>
       <c r="D15">
-        <v>31303.413</v>
+        <v>31471.028</v>
       </c>
       <c r="E15">
-        <v>36401.897</v>
+        <v>36214.232</v>
       </c>
       <c r="F15">
-        <v>2818.581</v>
+        <v>35757.546</v>
       </c>
       <c r="G15">
-        <v>2467.909</v>
+        <v>33224.955</v>
       </c>
       <c r="H15">
-        <v>3169.253</v>
+        <v>38290.136</v>
       </c>
       <c r="I15">
-        <v>1885660584.091</v>
+        <v>1783337373.026</v>
       </c>
       <c r="J15">
-        <v>1743662707.732</v>
+        <v>1658365804.004</v>
       </c>
       <c r="K15">
-        <v>2027658460.449</v>
+        <v>1908308942.049</v>
       </c>
       <c r="L15">
-        <v>374871331.539</v>
+        <v>4755753552.903</v>
       </c>
       <c r="M15">
-        <v>328231955.698</v>
+        <v>4418919024.773</v>
       </c>
       <c r="N15">
-        <v>421510707.38</v>
+        <v>5092588081.034</v>
       </c>
     </row>
     <row r="16">
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>7356.51</v>
+        <v>241.652</v>
       </c>
       <c r="D16">
-        <v>6656.967</v>
+        <v>223.743</v>
       </c>
       <c r="E16">
-        <v>8056.053</v>
+        <v>259.56</v>
       </c>
       <c r="F16">
-        <v>24868.454</v>
+        <v>147.433</v>
       </c>
       <c r="G16">
-        <v>22430.301</v>
+        <v>136.369</v>
       </c>
       <c r="H16">
-        <v>27306.606</v>
+        <v>158.496</v>
       </c>
       <c r="I16">
-        <v>108927845.465</v>
+        <v>7084992.971</v>
       </c>
       <c r="J16">
-        <v>98569715.222</v>
+        <v>6559934.658</v>
       </c>
       <c r="K16">
-        <v>119285975.707</v>
+        <v>7610051.284</v>
       </c>
       <c r="L16">
-        <v>3307504360.685</v>
+        <v>19608526.999</v>
       </c>
       <c r="M16">
-        <v>2983230078.54</v>
+        <v>18137074.389</v>
       </c>
       <c r="N16">
-        <v>3631778642.83</v>
+        <v>21079979.609</v>
       </c>
     </row>
     <row r="17">
@@ -1158,40 +1158,40 @@
         </is>
       </c>
       <c r="C17">
-        <v>12793.447</v>
+        <v>771.0940000000001</v>
       </c>
       <c r="D17">
-        <v>11718.86</v>
+        <v>721.885</v>
       </c>
       <c r="E17">
-        <v>13868.033</v>
+        <v>820.303</v>
       </c>
       <c r="F17">
-        <v>35755.606</v>
+        <v>459.798</v>
       </c>
       <c r="G17">
-        <v>32673.39</v>
+        <v>430.052</v>
       </c>
       <c r="H17">
-        <v>38837.822</v>
+        <v>489.544</v>
       </c>
       <c r="I17">
-        <v>189432563.873</v>
+        <v>22607709.279</v>
       </c>
       <c r="J17">
-        <v>173521156.445</v>
+        <v>21164958.166</v>
       </c>
       <c r="K17">
-        <v>205343971.301</v>
+        <v>24050460.392</v>
       </c>
       <c r="L17">
-        <v>4755495589.112</v>
+        <v>61153132.476</v>
       </c>
       <c r="M17">
-        <v>4345560867.017</v>
+        <v>57196971.369</v>
       </c>
       <c r="N17">
-        <v>5165430311.208</v>
+        <v>65109293.583</v>
       </c>
     </row>
     <row r="18">
@@ -1206,40 +1206,40 @@
         </is>
       </c>
       <c r="C18">
-        <v>20515.995</v>
+        <v>2130.988</v>
       </c>
       <c r="D18">
-        <v>18938.12</v>
+        <v>1998.701</v>
       </c>
       <c r="E18">
-        <v>22093.871</v>
+        <v>2263.275</v>
       </c>
       <c r="F18">
-        <v>46030.607</v>
+        <v>1185.567</v>
       </c>
       <c r="G18">
-        <v>42309.838</v>
+        <v>1109.942</v>
       </c>
       <c r="H18">
-        <v>49751.376</v>
+        <v>1261.191</v>
       </c>
       <c r="I18">
-        <v>303780343.288</v>
+        <v>62478430.991</v>
       </c>
       <c r="J18">
-        <v>280416737.934</v>
+        <v>58599903.015</v>
       </c>
       <c r="K18">
-        <v>327143948.641</v>
+        <v>66356958.967</v>
       </c>
       <c r="L18">
-        <v>6122070696.615</v>
+        <v>157680377.629</v>
       </c>
       <c r="M18">
-        <v>5627208449.944</v>
+        <v>147622311.219</v>
       </c>
       <c r="N18">
-        <v>6616932943.287</v>
+        <v>167738444.04</v>
       </c>
     </row>
     <row r="19">
@@ -1254,40 +1254,40 @@
         </is>
       </c>
       <c r="C19">
-        <v>25630.647</v>
+        <v>4241.089</v>
       </c>
       <c r="D19">
-        <v>24048.415</v>
+        <v>4021.276</v>
       </c>
       <c r="E19">
-        <v>27212.878</v>
+        <v>4460.903</v>
       </c>
       <c r="F19">
-        <v>41947.344</v>
+        <v>2193.595</v>
       </c>
       <c r="G19">
-        <v>39236.594</v>
+        <v>2078.93</v>
       </c>
       <c r="H19">
-        <v>44658.093</v>
+        <v>2308.259</v>
       </c>
       <c r="I19">
-        <v>379512987.81</v>
+        <v>124344501.042</v>
       </c>
       <c r="J19">
-        <v>356084884.632</v>
+        <v>117899788.077</v>
       </c>
       <c r="K19">
-        <v>402941090.988</v>
+        <v>130789214.008</v>
       </c>
       <c r="L19">
-        <v>5578996705.993</v>
+        <v>291748106.154</v>
       </c>
       <c r="M19">
-        <v>5218467046.215</v>
+        <v>276497742.004</v>
       </c>
       <c r="N19">
-        <v>5939526365.771</v>
+        <v>306998470.304</v>
       </c>
     </row>
     <row r="20">
@@ -1302,40 +1302,40 @@
         </is>
       </c>
       <c r="C20">
-        <v>32383.555</v>
+        <v>8643.766</v>
       </c>
       <c r="D20">
-        <v>30583.069</v>
+        <v>8196.686</v>
       </c>
       <c r="E20">
-        <v>34184.041</v>
+        <v>9090.844999999999</v>
       </c>
       <c r="F20">
-        <v>34175.531</v>
+        <v>4235.063</v>
       </c>
       <c r="G20">
-        <v>32175.233</v>
+        <v>4021.982</v>
       </c>
       <c r="H20">
-        <v>36175.829</v>
+        <v>4448.144</v>
       </c>
       <c r="I20">
-        <v>479503299.963</v>
+        <v>253426563.958</v>
       </c>
       <c r="J20">
-        <v>452843506.333</v>
+        <v>240318644.42</v>
       </c>
       <c r="K20">
-        <v>506163093.593</v>
+        <v>266534483.496</v>
       </c>
       <c r="L20">
-        <v>4545345590.93</v>
+        <v>563263353.1160001</v>
       </c>
       <c r="M20">
-        <v>4279305960.996</v>
+        <v>534923588.496</v>
       </c>
       <c r="N20">
-        <v>4811385220.863</v>
+        <v>591603117.7359999</v>
       </c>
     </row>
     <row r="21">
@@ -1350,40 +1350,40 @@
         </is>
       </c>
       <c r="C21">
-        <v>21578.016</v>
+        <v>8303.288</v>
       </c>
       <c r="D21">
-        <v>20217.485</v>
+        <v>7821.31</v>
       </c>
       <c r="E21">
-        <v>22938.548</v>
+        <v>8785.266</v>
       </c>
       <c r="F21">
-        <v>10657.159</v>
+        <v>3745.96</v>
       </c>
       <c r="G21">
-        <v>9950.887000000001</v>
+        <v>3533.375</v>
       </c>
       <c r="H21">
-        <v>11363.432</v>
+        <v>3958.546</v>
       </c>
       <c r="I21">
-        <v>319505688.519</v>
+        <v>243444106.373</v>
       </c>
       <c r="J21">
-        <v>299360298.133</v>
+        <v>229313000.116</v>
       </c>
       <c r="K21">
-        <v>339651078.905</v>
+        <v>257575212.63</v>
       </c>
       <c r="L21">
-        <v>1417402180.426</v>
+        <v>498212740.519</v>
       </c>
       <c r="M21">
-        <v>1323467922.167</v>
+        <v>469938907.786</v>
       </c>
       <c r="N21">
-        <v>1511336438.685</v>
+        <v>526486573.253</v>
       </c>
     </row>
     <row r="22">
@@ -1398,40 +1398,40 @@
         </is>
       </c>
       <c r="C22">
-        <v>9909.008</v>
+        <v>5461.37</v>
       </c>
       <c r="D22">
-        <v>8978.594999999999</v>
+        <v>5028.432</v>
       </c>
       <c r="E22">
-        <v>10839.42</v>
+        <v>5894.308</v>
       </c>
       <c r="F22">
-        <v>636.691</v>
+        <v>1889.921</v>
       </c>
       <c r="G22">
-        <v>541.711</v>
+        <v>1744.671</v>
       </c>
       <c r="H22">
-        <v>731.671</v>
+        <v>2035.17</v>
       </c>
       <c r="I22">
-        <v>146722674.761</v>
+        <v>160121905.302</v>
       </c>
       <c r="J22">
-        <v>132946061.075</v>
+        <v>147428598.307</v>
       </c>
       <c r="K22">
-        <v>160499288.446</v>
+        <v>172815212.297</v>
       </c>
       <c r="L22">
-        <v>84679912.27599999</v>
+        <v>251359445.593</v>
       </c>
       <c r="M22">
-        <v>72047518.44499999</v>
+        <v>232041266.084</v>
       </c>
       <c r="N22">
-        <v>97312306.10699999</v>
+        <v>270677625.103</v>
       </c>
     </row>
     <row r="23">
@@ -1446,40 +1446,40 @@
         </is>
       </c>
       <c r="C23">
-        <v>1567.994</v>
+        <v>1147.391</v>
       </c>
       <c r="D23">
-        <v>1437.516</v>
+        <v>1061.586</v>
       </c>
       <c r="E23">
-        <v>1698.471</v>
+        <v>1233.197</v>
       </c>
       <c r="F23">
-        <v>6330.994</v>
+        <v>633.997</v>
       </c>
       <c r="G23">
-        <v>5795.312</v>
+        <v>586.12</v>
       </c>
       <c r="H23">
-        <v>6866.675</v>
+        <v>681.874</v>
       </c>
       <c r="I23">
-        <v>117914687.97</v>
+        <v>44978893.615</v>
       </c>
       <c r="J23">
-        <v>108102657.953</v>
+        <v>41615244.296</v>
       </c>
       <c r="K23">
-        <v>127726717.987</v>
+        <v>48342542.934</v>
       </c>
       <c r="L23">
-        <v>842022163.099</v>
+        <v>84321616.484</v>
       </c>
       <c r="M23">
-        <v>770776533.448</v>
+        <v>77954000.27599999</v>
       </c>
       <c r="N23">
-        <v>913267792.751</v>
+        <v>90689232.693</v>
       </c>
     </row>
     <row r="24">
@@ -1494,40 +1494,40 @@
         </is>
       </c>
       <c r="C24">
-        <v>2835.908</v>
+        <v>2069.618</v>
       </c>
       <c r="D24">
-        <v>2631.084</v>
+        <v>1935.427</v>
       </c>
       <c r="E24">
-        <v>3040.732</v>
+        <v>2203.809</v>
       </c>
       <c r="F24">
-        <v>9286.025</v>
+        <v>1977.724</v>
       </c>
       <c r="G24">
-        <v>8616.334999999999</v>
+        <v>1849.265</v>
       </c>
       <c r="H24">
-        <v>9955.715</v>
+        <v>2106.183</v>
       </c>
       <c r="I24">
-        <v>213263129.195</v>
+        <v>81131077.242</v>
       </c>
       <c r="J24">
-        <v>197860176.032</v>
+        <v>75870654.77500001</v>
       </c>
       <c r="K24">
-        <v>228666082.357</v>
+        <v>86391499.70900001</v>
       </c>
       <c r="L24">
-        <v>1235041325.998</v>
+        <v>263037268.46</v>
       </c>
       <c r="M24">
-        <v>1145972616.473</v>
+        <v>245952262.697</v>
       </c>
       <c r="N24">
-        <v>1324110035.523</v>
+        <v>280122274.222</v>
       </c>
     </row>
     <row r="25">
@@ -1542,40 +1542,40 @@
         </is>
       </c>
       <c r="C25">
-        <v>4851.449</v>
+        <v>3508.946</v>
       </c>
       <c r="D25">
-        <v>4499.789</v>
+        <v>3282.894</v>
       </c>
       <c r="E25">
-        <v>5203.109</v>
+        <v>3734.998</v>
       </c>
       <c r="F25">
-        <v>12615.382</v>
+        <v>4421.378</v>
       </c>
       <c r="G25">
-        <v>11696.786</v>
+        <v>4134.068</v>
       </c>
       <c r="H25">
-        <v>13533.978</v>
+        <v>4708.689</v>
       </c>
       <c r="I25">
-        <v>364833806.795</v>
+        <v>137554206.137</v>
       </c>
       <c r="J25">
-        <v>338388599.694</v>
+        <v>128692737.238</v>
       </c>
       <c r="K25">
-        <v>391279013.896</v>
+        <v>146415675.037</v>
       </c>
       <c r="L25">
-        <v>1677845764.383</v>
+        <v>588043328.881</v>
       </c>
       <c r="M25">
-        <v>1555672489.172</v>
+        <v>549830999.48</v>
       </c>
       <c r="N25">
-        <v>1800019039.594</v>
+        <v>626255658.281</v>
       </c>
     </row>
     <row r="26">
@@ -1590,40 +1590,40 @@
         </is>
       </c>
       <c r="C26">
-        <v>7114.591</v>
+        <v>5260.883</v>
       </c>
       <c r="D26">
-        <v>6701.023</v>
+        <v>4990.017</v>
       </c>
       <c r="E26">
-        <v>7528.159</v>
+        <v>5531.749</v>
       </c>
       <c r="F26">
-        <v>13699.571</v>
+        <v>6513.847</v>
       </c>
       <c r="G26">
-        <v>12898.586</v>
+        <v>6165.553</v>
       </c>
       <c r="H26">
-        <v>14500.556</v>
+        <v>6862.14</v>
       </c>
       <c r="I26">
-        <v>535024365.025</v>
+        <v>206231882.26</v>
       </c>
       <c r="J26">
-        <v>503923644.851</v>
+        <v>195613658.325</v>
       </c>
       <c r="K26">
-        <v>566125085.2</v>
+        <v>216850106.194</v>
       </c>
       <c r="L26">
-        <v>1822042954.565</v>
+        <v>866341593.49</v>
       </c>
       <c r="M26">
-        <v>1715512003.726</v>
+        <v>820018606.969</v>
       </c>
       <c r="N26">
-        <v>1928573905.404</v>
+        <v>912664580.011</v>
       </c>
     </row>
     <row r="27">
@@ -1638,40 +1638,40 @@
         </is>
       </c>
       <c r="C27">
-        <v>8543.971</v>
+        <v>6300.45</v>
       </c>
       <c r="D27">
-        <v>8078.529</v>
+        <v>5999.094</v>
       </c>
       <c r="E27">
-        <v>9009.414000000001</v>
+        <v>6601.806</v>
       </c>
       <c r="F27">
-        <v>10978.865</v>
+        <v>10675.17</v>
       </c>
       <c r="G27">
-        <v>10357.43</v>
+        <v>10131.782</v>
       </c>
       <c r="H27">
-        <v>11600.3</v>
+        <v>11218.557</v>
       </c>
       <c r="I27">
-        <v>642515177.284</v>
+        <v>246983936.65</v>
       </c>
       <c r="J27">
-        <v>607513446.173</v>
+        <v>235170484.697</v>
       </c>
       <c r="K27">
-        <v>677516908.396</v>
+        <v>258797388.602</v>
       </c>
       <c r="L27">
-        <v>1460189108.779</v>
+        <v>1419797563.638</v>
       </c>
       <c r="M27">
-        <v>1377538254.776</v>
+        <v>1347527051.36</v>
       </c>
       <c r="N27">
-        <v>1542839962.782</v>
+        <v>1492068075.915</v>
       </c>
     </row>
     <row r="28">
@@ -1686,40 +1686,40 @@
         </is>
       </c>
       <c r="C28">
-        <v>2734.25</v>
+        <v>2065.78</v>
       </c>
       <c r="D28">
-        <v>2566.836</v>
+        <v>1955.358</v>
       </c>
       <c r="E28">
-        <v>2901.663</v>
+        <v>2176.201</v>
       </c>
       <c r="F28">
-        <v>1756.839</v>
+        <v>8713.326999999999</v>
       </c>
       <c r="G28">
-        <v>1639.189</v>
+        <v>8210.612999999999</v>
       </c>
       <c r="H28">
-        <v>1874.489</v>
+        <v>9216.040999999999</v>
       </c>
       <c r="I28">
-        <v>205618321.768</v>
+        <v>80980622.995</v>
       </c>
       <c r="J28">
-        <v>193028651.947</v>
+        <v>76651992.32099999</v>
       </c>
       <c r="K28">
-        <v>218207991.588</v>
+        <v>85309253.67</v>
       </c>
       <c r="L28">
-        <v>233659568.822</v>
+        <v>1158872543.478</v>
       </c>
       <c r="M28">
-        <v>218012078.018</v>
+        <v>1092011578.316</v>
       </c>
       <c r="N28">
-        <v>249307059.627</v>
+        <v>1225733508.64</v>
       </c>
     </row>
     <row r="29">
@@ -1734,40 +1734,40 @@
         </is>
       </c>
       <c r="C29">
-        <v>126.49</v>
+        <v>106.822</v>
       </c>
       <c r="D29">
-        <v>115.035</v>
+        <v>98.83799999999999</v>
       </c>
       <c r="E29">
-        <v>137.945</v>
+        <v>114.807</v>
       </c>
       <c r="F29">
-        <v>13.68</v>
+        <v>4634.835</v>
       </c>
       <c r="G29">
-        <v>11.605</v>
+        <v>4254.858</v>
       </c>
       <c r="H29">
-        <v>15.754</v>
+        <v>5014.812</v>
       </c>
       <c r="I29">
-        <v>9512159.839</v>
+        <v>4187537.306</v>
       </c>
       <c r="J29">
-        <v>8650723.774</v>
+        <v>3874531.425</v>
       </c>
       <c r="K29">
-        <v>10373595.904</v>
+        <v>4500543.187</v>
       </c>
       <c r="L29">
-        <v>1819386.643</v>
+        <v>616433068.299</v>
       </c>
       <c r="M29">
-        <v>1543518.308</v>
+        <v>565896135.669</v>
       </c>
       <c r="N29">
-        <v>2095254.979</v>
+        <v>666970000.929</v>
       </c>
     </row>
     <row r="30">
@@ -1878,40 +1878,40 @@
         </is>
       </c>
       <c r="C32">
-        <v>685.956</v>
+        <v>595.395</v>
       </c>
       <c r="D32">
-        <v>645.516</v>
+        <v>560.101</v>
       </c>
       <c r="E32">
-        <v>726.397</v>
+        <v>630.688</v>
       </c>
       <c r="F32">
-        <v>5503.229</v>
+        <v>432.865</v>
       </c>
       <c r="G32">
-        <v>5168.687</v>
+        <v>406.987</v>
       </c>
       <c r="H32">
-        <v>5837.772</v>
+        <v>458.743</v>
       </c>
       <c r="I32">
-        <v>11550815.312</v>
+        <v>9912134.016000001</v>
       </c>
       <c r="J32">
-        <v>10869835.509</v>
+        <v>9324568.747</v>
       </c>
       <c r="K32">
-        <v>12231795.116</v>
+        <v>10499699.285</v>
       </c>
       <c r="L32">
-        <v>731929510.141</v>
+        <v>57571028.475</v>
       </c>
       <c r="M32">
-        <v>687435320.698</v>
+        <v>54129247.741</v>
       </c>
       <c r="N32">
-        <v>776423699.5829999</v>
+        <v>61012809.209</v>
       </c>
     </row>
     <row r="33">
@@ -1926,40 +1926,40 @@
         </is>
       </c>
       <c r="C33">
-        <v>1255.321</v>
+        <v>1107.488</v>
       </c>
       <c r="D33">
-        <v>1192.687</v>
+        <v>1052.24</v>
       </c>
       <c r="E33">
-        <v>1317.956</v>
+        <v>1162.737</v>
       </c>
       <c r="F33">
-        <v>7413.339</v>
+        <v>1926.472</v>
       </c>
       <c r="G33">
-        <v>7034.502</v>
+        <v>1828.456</v>
       </c>
       <c r="H33">
-        <v>7792.176</v>
+        <v>2024.488</v>
       </c>
       <c r="I33">
-        <v>21138354.064</v>
+        <v>18437467.93</v>
       </c>
       <c r="J33">
-        <v>20083652.478</v>
+        <v>17517689.241</v>
       </c>
       <c r="K33">
-        <v>22193055.651</v>
+        <v>19357246.62</v>
       </c>
       <c r="L33">
-        <v>985974107.359</v>
+        <v>256220756.554</v>
       </c>
       <c r="M33">
-        <v>935588815.293</v>
+        <v>243184654.779</v>
       </c>
       <c r="N33">
-        <v>1036359399.425</v>
+        <v>269256858.33</v>
       </c>
     </row>
     <row r="34">
@@ -1974,40 +1974,40 @@
         </is>
       </c>
       <c r="C34">
-        <v>6820.68</v>
+        <v>5986.57</v>
       </c>
       <c r="D34">
-        <v>6511.697</v>
+        <v>5718.457</v>
       </c>
       <c r="E34">
-        <v>7129.663</v>
+        <v>6254.684</v>
       </c>
       <c r="F34">
-        <v>26619.397</v>
+        <v>6330.032</v>
       </c>
       <c r="G34">
-        <v>25354.009</v>
+        <v>6043.993</v>
       </c>
       <c r="H34">
-        <v>27884.785</v>
+        <v>6616.071</v>
       </c>
       <c r="I34">
-        <v>114853427.149</v>
+        <v>99664424.41599999</v>
       </c>
       <c r="J34">
-        <v>109650464.753</v>
+        <v>95200871.53300001</v>
       </c>
       <c r="K34">
-        <v>120056389.546</v>
+        <v>104127977.299</v>
       </c>
       <c r="L34">
-        <v>3540379798.892</v>
+        <v>841894311.465</v>
       </c>
       <c r="M34">
-        <v>3372083161.508</v>
+        <v>803851115.7359999</v>
       </c>
       <c r="N34">
-        <v>3708676436.277</v>
+        <v>879937507.194</v>
       </c>
     </row>
     <row r="35">
@@ -2022,40 +2022,40 @@
         </is>
       </c>
       <c r="C35">
-        <v>17613.911</v>
+        <v>15844.154</v>
       </c>
       <c r="D35">
-        <v>16727.967</v>
+        <v>15062.305</v>
       </c>
       <c r="E35">
-        <v>18499.855</v>
+        <v>16626.004</v>
       </c>
       <c r="F35">
-        <v>34616.427</v>
+        <v>17563.998</v>
       </c>
       <c r="G35">
-        <v>32683.198</v>
+        <v>16687.877</v>
       </c>
       <c r="H35">
-        <v>36549.657</v>
+        <v>18440.119</v>
       </c>
       <c r="I35">
-        <v>296600640.848</v>
+        <v>263773481.311</v>
       </c>
       <c r="J35">
-        <v>281682230.311</v>
+        <v>250757252.413</v>
       </c>
       <c r="K35">
-        <v>311519051.385</v>
+        <v>276789710.21</v>
       </c>
       <c r="L35">
-        <v>4603984843.649</v>
+        <v>2336011692.26</v>
       </c>
       <c r="M35">
-        <v>4346865297.747</v>
+        <v>2219487596.15</v>
       </c>
       <c r="N35">
-        <v>4861104389.551</v>
+        <v>2452535788.371</v>
       </c>
     </row>
     <row r="36">
@@ -2070,40 +2070,40 @@
         </is>
       </c>
       <c r="C36">
-        <v>24689.65</v>
+        <v>24728.8</v>
       </c>
       <c r="D36">
-        <v>22887.761</v>
+        <v>23053.37</v>
       </c>
       <c r="E36">
-        <v>26491.538</v>
+        <v>26404.231</v>
       </c>
       <c r="F36">
-        <v>7649.673</v>
+        <v>28971.925</v>
       </c>
       <c r="G36">
-        <v>6710.328</v>
+        <v>26991.888</v>
       </c>
       <c r="H36">
-        <v>8589.019</v>
+        <v>30951.963</v>
       </c>
       <c r="I36">
-        <v>415749009.822</v>
+        <v>411685068.301</v>
       </c>
       <c r="J36">
-        <v>385407012.341</v>
+        <v>383792496.918</v>
       </c>
       <c r="K36">
-        <v>446091007.302</v>
+        <v>439577639.683</v>
       </c>
       <c r="L36">
-        <v>1017406569.716</v>
+        <v>3853266066.025</v>
       </c>
       <c r="M36">
-        <v>892473589.057</v>
+        <v>3589921073.99</v>
       </c>
       <c r="N36">
-        <v>1142339550.375</v>
+        <v>4116611058.06</v>
       </c>
     </row>
     <row r="37">
@@ -2118,22 +2118,22 @@
         </is>
       </c>
       <c r="C37">
-        <v>70737.822</v>
+        <v>61311.409</v>
       </c>
       <c r="D37">
-        <v>65627.673</v>
+        <v>57157.359</v>
       </c>
       <c r="E37">
-        <v>75847.97</v>
+        <v>65465.458</v>
       </c>
       <c r="F37">
-        <v>39961.206</v>
+        <v>39625.67</v>
       </c>
       <c r="G37">
-        <v>36861.745</v>
+        <v>36847.798</v>
       </c>
       <c r="H37">
-        <v>43060.667</v>
+        <v>42403.541</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2145,13 +2145,13 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>5314840367.571</v>
+        <v>5270214057.813</v>
       </c>
       <c r="M37">
-        <v>4902612075.078</v>
+        <v>4900757108.548</v>
       </c>
       <c r="N37">
-        <v>5727068660.063</v>
+        <v>5639671007.077</v>
       </c>
     </row>
     <row r="38">
@@ -2166,22 +2166,22 @@
         </is>
       </c>
       <c r="C38">
-        <v>80429.639</v>
+        <v>68742.446</v>
       </c>
       <c r="D38">
-        <v>75343.414</v>
+        <v>64663.92</v>
       </c>
       <c r="E38">
-        <v>85515.864</v>
+        <v>72820.97199999999</v>
       </c>
       <c r="F38">
-        <v>37873.067</v>
+        <v>37036.399</v>
       </c>
       <c r="G38">
-        <v>35332.851</v>
+        <v>34777.973</v>
       </c>
       <c r="H38">
-        <v>40413.284</v>
+        <v>39294.826</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2193,13 +2193,13 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>5037117973.823</v>
+        <v>4925841125.854</v>
       </c>
       <c r="M38">
-        <v>4699269188.895</v>
+        <v>4625470457.304</v>
       </c>
       <c r="N38">
-        <v>5374966758.75</v>
+        <v>5226211794.404</v>
       </c>
     </row>
     <row r="39">
@@ -2214,22 +2214,22 @@
         </is>
       </c>
       <c r="C39">
-        <v>92189.07000000001</v>
+        <v>78297.71400000001</v>
       </c>
       <c r="D39">
-        <v>86681.49400000001</v>
+        <v>73869.796</v>
       </c>
       <c r="E39">
-        <v>97696.64599999999</v>
+        <v>82725.633</v>
       </c>
       <c r="F39">
-        <v>35883.697</v>
+        <v>34615.149</v>
       </c>
       <c r="G39">
-        <v>33536.324</v>
+        <v>32550.131</v>
       </c>
       <c r="H39">
-        <v>38231.069</v>
+        <v>36680.166</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2241,13 +2241,13 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>4772531638.58</v>
+        <v>4603814783.776</v>
       </c>
       <c r="M39">
-        <v>4460331125.363</v>
+        <v>4329167487.073</v>
       </c>
       <c r="N39">
-        <v>5084732151.798</v>
+        <v>4878462080.48</v>
       </c>
     </row>
     <row r="40">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="C40">
-        <v>85874.11900000001</v>
+        <v>72746.558</v>
       </c>
       <c r="D40">
-        <v>81494.77499999999</v>
+        <v>69246.852</v>
       </c>
       <c r="E40">
-        <v>90253.46400000001</v>
+        <v>76246.26300000001</v>
       </c>
       <c r="F40">
-        <v>25504.954</v>
+        <v>24633.046</v>
       </c>
       <c r="G40">
-        <v>24078.476</v>
+        <v>23379.915</v>
       </c>
       <c r="H40">
-        <v>26931.432</v>
+        <v>25886.177</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2289,13 +2289,13 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>3392158912.953</v>
+        <v>3276195087.628</v>
       </c>
       <c r="M40">
-        <v>3202437363.982</v>
+        <v>3109528633.273</v>
       </c>
       <c r="N40">
-        <v>3581880461.925</v>
+        <v>3442861541.983</v>
       </c>
     </row>
     <row r="41">
@@ -2310,22 +2310,22 @@
         </is>
       </c>
       <c r="C41">
-        <v>90653.107</v>
+        <v>76946.569</v>
       </c>
       <c r="D41">
-        <v>86377.65700000001</v>
+        <v>73528.231</v>
       </c>
       <c r="E41">
-        <v>94928.557</v>
+        <v>80364.90700000001</v>
       </c>
       <c r="F41">
-        <v>18382.225</v>
+        <v>17712.306</v>
       </c>
       <c r="G41">
-        <v>17399.685</v>
+        <v>16853.224</v>
       </c>
       <c r="H41">
-        <v>19364.766</v>
+        <v>18571.389</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2337,13 +2337,13 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>2444835991.396</v>
+        <v>2355736754.971</v>
       </c>
       <c r="M41">
-        <v>2314158053.742</v>
+        <v>2241478777.425</v>
       </c>
       <c r="N41">
-        <v>2575513929.049</v>
+        <v>2469994732.517</v>
       </c>
     </row>
     <row r="42">
@@ -2358,22 +2358,22 @@
         </is>
       </c>
       <c r="C42">
-        <v>60378.06</v>
+        <v>52160.774</v>
       </c>
       <c r="D42">
-        <v>57173.572</v>
+        <v>49579.215</v>
       </c>
       <c r="E42">
-        <v>63582.548</v>
+        <v>54742.333</v>
       </c>
       <c r="F42">
-        <v>6464.244</v>
+        <v>6379.708</v>
       </c>
       <c r="G42">
-        <v>6052.539</v>
+        <v>6013.634</v>
       </c>
       <c r="H42">
-        <v>6875.949</v>
+        <v>6745.782</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2385,13 +2385,13 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>859744460.263</v>
+        <v>848501155.377</v>
       </c>
       <c r="M42">
-        <v>804987691.1619999</v>
+        <v>799813280.186</v>
       </c>
       <c r="N42">
-        <v>914501229.364</v>
+        <v>897189030.568</v>
       </c>
     </row>
     <row r="43">
@@ -2406,22 +2406,22 @@
         </is>
       </c>
       <c r="C43">
-        <v>31335.51</v>
+        <v>29667.678</v>
       </c>
       <c r="D43">
-        <v>28955.614</v>
+        <v>27661.85</v>
       </c>
       <c r="E43">
-        <v>33715.405</v>
+        <v>31673.506</v>
       </c>
       <c r="F43">
-        <v>615.528</v>
+        <v>645.712</v>
       </c>
       <c r="G43">
-        <v>535.478</v>
+        <v>573.112</v>
       </c>
       <c r="H43">
-        <v>695.579</v>
+        <v>718.312</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2433,13 +2433,13 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>81865263.53399999</v>
+        <v>85879679.14300001</v>
       </c>
       <c r="M43">
-        <v>71218586.54700001</v>
+        <v>76223901.23</v>
       </c>
       <c r="N43">
-        <v>92511940.522</v>
+        <v>95535457.05599999</v>
       </c>
     </row>
   </sheetData>
